--- a/dataset/Evaluacióndelaaplicaciónpropuesta33respuestas.xlsx
+++ b/dataset/Evaluacióndelaaplicaciónpropuesta33respuestas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/487740a2c6e0bf12/Profesional/PUBLICACIONES/DUA_VIRTUS/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{6C502984-37C1-4D30-8F1F-5DF73AAEB220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A45B7E77-0BAF-4524-9E84-68C346056B2D}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{6C502984-37C1-4D30-8F1F-5DF73AAEB220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F4A8C37-9929-4E45-91CD-18702CC4D142}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="2370" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="102">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -123,9 +123,6 @@
     <t>Las respuestas proporcionadas en este formulario se conservarán de forma anónima, por lo que su identidad no será conocida, y por ende tampoco revelada. Conociendo esto, ¿otorga usted su consentimiento para incluir estos datos en el análisis pertinente cuyos resultados serán parte del trabajo de titulación de Geovanny Brito Casanova y eventualmente podrían ser parte de una publicación académica/científica/tecnológica?</t>
   </si>
   <si>
-    <t>1 Luis Rosado</t>
-  </si>
-  <si>
     <t>Masculino</t>
   </si>
   <si>
@@ -144,9 +141,6 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>2 Maribel Arzube</t>
-  </si>
-  <si>
     <t>Femenino</t>
   </si>
   <si>
@@ -162,27 +156,18 @@
     <t>Muy interesante para el uso de quienes inician en el manejo de la tecnología.</t>
   </si>
   <si>
-    <t>3 Jose Mestanza</t>
-  </si>
-  <si>
     <t>El audio deberia ser mas lento para que las personas puedan entender mejor</t>
   </si>
   <si>
     <t>Es una aplicación que podria ayudar mucho a las personas y podria mejorar mucho la educaicón</t>
   </si>
   <si>
-    <t>4 Jeniffer López</t>
-  </si>
-  <si>
     <t xml:space="preserve">Noto la aplicación con un diseño bastante serio, podría tener como en youtube que su diseño cambia para kids y usuarios normales, muy aparte de la personalización mostrada </t>
   </si>
   <si>
     <t xml:space="preserve">Muy interesante y novedosa la aplicación, fue divertido su interacción y los múltiples medios de posibilidades que da </t>
   </si>
   <si>
-    <t>5 Mayra López</t>
-  </si>
-  <si>
     <t>Emprendor@</t>
   </si>
   <si>
@@ -192,9 +177,6 @@
     <t>Muy didáctica e interesante, como una propuesta está excelente</t>
   </si>
   <si>
-    <t>6 Emiliana López</t>
-  </si>
-  <si>
     <t>Enfermera</t>
   </si>
   <si>
@@ -204,9 +186,6 @@
     <t xml:space="preserve">La idea es muy buena, tengo 2 hijos de 5 y 1 año, la de 5 años estuvo alado mío y ahora quiere usar la aplicación. </t>
   </si>
   <si>
-    <t>7 Jose Toapanta</t>
-  </si>
-  <si>
     <t>Creo que sí, problemas de visión.</t>
   </si>
   <si>
@@ -216,18 +195,12 @@
     <t>Es muy interactiva, me gusto ver las diferentes maneras de contestar las preguntas o resolver las evaluaciones, al igual que sus funciones de pistas, narrador de preguntas, etc.</t>
   </si>
   <si>
-    <t>8 Jasury Mazacon</t>
-  </si>
-  <si>
     <t>No se pueden contemplar todas las funcionalidades desde el móvil</t>
   </si>
   <si>
     <t xml:space="preserve">Si el SGA fuera así, sería más divertido </t>
   </si>
   <si>
-    <t>9 Wladimir Paredes</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -237,72 +210,48 @@
     <t>Aplica correctamente el concepto de inclusividad por medio de accesibilidad.</t>
   </si>
   <si>
-    <t>10 Valeria Torres</t>
-  </si>
-  <si>
     <t>No lo creo necesario.</t>
   </si>
   <si>
     <t>Está bien distribuida y tiene muchas opciones que facilitan su uso.</t>
   </si>
   <si>
-    <t>11 Mayra Plasencio</t>
-  </si>
-  <si>
     <t xml:space="preserve">Se podría realizar más testeos de la aplicación a medida que se vaya actualizando sus versiones para obtener una mayor captación de las necesidades de usabilidad. </t>
   </si>
   <si>
     <t xml:space="preserve">Muy acertada la idea. </t>
   </si>
   <si>
-    <t>12 Anthony Pachay</t>
-  </si>
-  <si>
     <t>Integrar nuevas formas de interacción</t>
   </si>
   <si>
     <t>Es una excelente aplicación</t>
   </si>
   <si>
-    <t>13 Juan Carlos Caviedes</t>
-  </si>
-  <si>
     <t>No, me parece que esta genial</t>
   </si>
   <si>
     <t>muy buena</t>
   </si>
   <si>
-    <t>14 Duval Carvajal</t>
-  </si>
-  <si>
     <t>Se podria mejorar creando una intefaz que permira probar las evaluaciones sin registrarse</t>
   </si>
   <si>
     <t>Me parece muy interesante, al momento de evaluar a los usuarios</t>
   </si>
   <si>
-    <t>15 Willy Rosado</t>
-  </si>
-  <si>
     <t>Siento que la aplicación apunta a todos y la forma en la cual permite el desarrollo de los conocimientos es la adecuada.</t>
   </si>
   <si>
     <t>Este Software tiene muchas formas de responder y se siente muy intuitivo y me gustaría que el sistema de mi universidad tuviera las mismas bases para dejar atrás los sistemas complejos y arcaicos y seguir el ejemplo de Virtus</t>
   </si>
   <si>
-    <t>16 Karelys Hidalgo</t>
-  </si>
-  <si>
     <t>Terminar las funciones pendientes como lo del avatar</t>
   </si>
   <si>
     <t>Mi criterio es que es una idea que no había ni concebido, una nueva manera de poder aprender.</t>
   </si>
   <si>
-    <t>17 Geiner Zavala</t>
-  </si>
-  <si>
     <t>administrador</t>
   </si>
   <si>
@@ -312,36 +261,24 @@
     <t>La interfaz me recuerda al BlackBoard, una plataforma que trabaja de manera privada lo cual lo hace más sencillo de utilizar para aquellos que la conocen.</t>
   </si>
   <si>
-    <t>18 Brittany Cedeño</t>
-  </si>
-  <si>
     <t xml:space="preserve">todo esta bien </t>
   </si>
   <si>
     <t xml:space="preserve">esta aplicacion  seria muy buena si estaria en la escuela Fatima </t>
   </si>
   <si>
-    <t>19 Jordy Rivas</t>
-  </si>
-  <si>
     <t>Que se pueda silenciar al bot que esta narrando la pregunta de forma rápida</t>
   </si>
   <si>
     <t>La aplicación mostró recursos para poder ver el tipo de ayuda que ofrece a los diferentes tipos de usuarios, ya sea que tengan algún tipo de discapacidad o no.</t>
   </si>
   <si>
-    <t>20 Patricio Boza</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ninguna </t>
   </si>
   <si>
     <t>Me parece muy bien estructurada, muy acorde para todas las edades</t>
   </si>
   <si>
-    <t xml:space="preserve">21 Estela Cedeño </t>
-  </si>
-  <si>
     <t>Ingeniera Agropecuaria</t>
   </si>
   <si>
@@ -351,42 +288,27 @@
     <t>Excelente</t>
   </si>
   <si>
-    <t>22 Kathya Cedeño Arzube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ninguna recomendación </t>
   </si>
   <si>
     <t>Me pareció muy práctica e inclusiva</t>
   </si>
   <si>
-    <t xml:space="preserve">23 Nara Boza </t>
-  </si>
-  <si>
     <t xml:space="preserve">Una aplicación móvil </t>
   </si>
   <si>
     <t>Es una aplicación novedosa y fácil de usar</t>
   </si>
   <si>
-    <t>24 Evelyn Bailon</t>
-  </si>
-  <si>
     <t>esta muy bien la aplicacion</t>
   </si>
   <si>
-    <t>25 Victor Romero</t>
-  </si>
-  <si>
     <t>Física</t>
   </si>
   <si>
     <t>Ninguna observación.</t>
   </si>
   <si>
-    <t>26 Orlando Brito</t>
-  </si>
-  <si>
     <t>Master en Ciberseguridad</t>
   </si>
   <si>
@@ -396,33 +318,21 @@
     <t>Para ser una primera versión está muy completa</t>
   </si>
   <si>
-    <t>27 Dayanna Vélez</t>
-  </si>
-  <si>
     <t>.</t>
   </si>
   <si>
-    <t>28 Vivian Zamora</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mejorar el UI UX </t>
   </si>
   <si>
     <t>Como prototipo muy completo</t>
   </si>
   <si>
-    <t>29 María Méndez</t>
-  </si>
-  <si>
     <t xml:space="preserve">Modo oscuro integrado, sin necesidad de extensión </t>
   </si>
   <si>
     <t xml:space="preserve">Aplicación con gran futuro </t>
   </si>
   <si>
-    <t>30 Michelle Solano</t>
-  </si>
-  <si>
     <t>Poder desactivar ciertas funciones que el usuario considere no necesario</t>
   </si>
   <si>
@@ -430,15 +340,6 @@
   </si>
   <si>
     <t xml:space="preserve">. </t>
-  </si>
-  <si>
-    <t>31 Participante reconstruido 31</t>
-  </si>
-  <si>
-    <t>32 Participante reconstruido 32</t>
-  </si>
-  <si>
-    <t>33 Participante reconstruido 33</t>
   </si>
 </sst>
 </file>
@@ -499,6 +400,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -792,23 +697,23 @@
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>29</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>44833.9870347338</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>23</v>
       </c>
       <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
         <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -874,33 +779,33 @@
         <v>5</v>
       </c>
       <c r="AE2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF2" t="s">
         <v>33</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>34</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>36</v>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3" s="2">
         <v>44834.017301898144</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3">
         <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -966,33 +871,33 @@
         <v>5</v>
       </c>
       <c r="AE3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AG3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>42</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>44834.046943969908</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>23</v>
       </c>
       <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
         <v>31</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1058,33 +963,33 @@
         <v>5</v>
       </c>
       <c r="AE4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AF4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AG4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>45</v>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="B5" s="2">
         <v>44834.058142164351</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>23</v>
       </c>
       <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
         <v>31</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1150,33 +1055,33 @@
         <v>5</v>
       </c>
       <c r="AE5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="AG5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>48</v>
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6" s="2">
         <v>44834.066450150465</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1242,33 +1147,33 @@
         <v>5</v>
       </c>
       <c r="AE6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="AG6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>52</v>
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>44834.073119155088</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7">
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1334,33 +1239,33 @@
         <v>5</v>
       </c>
       <c r="AE7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="AF7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="AG7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>56</v>
+      <c r="A8">
+        <v>7</v>
       </c>
       <c r="B8" s="2">
         <v>44834.100271863426</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8">
         <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1426,33 +1331,33 @@
         <v>4</v>
       </c>
       <c r="AE8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="AF8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AG8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>60</v>
+      <c r="A9">
+        <v>8</v>
       </c>
       <c r="B9" s="2">
         <v>44834.899482094908</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <v>23</v>
       </c>
       <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
         <v>31</v>
-      </c>
-      <c r="F9" t="s">
-        <v>32</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1518,33 +1423,33 @@
         <v>5</v>
       </c>
       <c r="AE9" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AF9" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="AG9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>63</v>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="B10" s="2">
         <v>44834.935226261572</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1610,34 +1515,34 @@
         <v>5</v>
       </c>
       <c r="AE10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="AF10" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="AG10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>67</v>
+      <c r="A11">
+        <v>10</v>
       </c>
       <c r="B11" s="2">
         <v>44834.941349386572</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11">
         <v>22</v>
       </c>
       <c r="E11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
         <v>31</v>
       </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
       <c r="G11">
         <v>5</v>
       </c>
@@ -1702,33 +1607,33 @@
         <v>5</v>
       </c>
       <c r="AE11" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="AF11" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="AG11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>70</v>
+      <c r="A12">
+        <v>11</v>
       </c>
       <c r="B12" s="2">
         <v>44834.9442021875</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12">
         <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -1794,33 +1699,33 @@
         <v>5</v>
       </c>
       <c r="AE12" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="AG12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
+      <c r="A13">
+        <v>12</v>
       </c>
       <c r="B13" s="2">
         <v>44834.950211250005</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1886,33 +1791,33 @@
         <v>5</v>
       </c>
       <c r="AE13" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="AF13" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="AG13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>76</v>
+      <c r="A14">
+        <v>13</v>
       </c>
       <c r="B14" s="2">
         <v>44834.989193634261</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -1978,33 +1883,33 @@
         <v>5</v>
       </c>
       <c r="AE14" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="AF14" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="AG14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>79</v>
+      <c r="A15">
+        <v>14</v>
       </c>
       <c r="B15" s="2">
         <v>44834.99700747685</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15">
         <v>22</v>
       </c>
       <c r="E15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" t="s">
         <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>32</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -2070,34 +1975,34 @@
         <v>4</v>
       </c>
       <c r="AE15" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="AF15" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="AG15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>82</v>
+      <c r="A16">
+        <v>15</v>
       </c>
       <c r="B16" s="2">
         <v>44835.678123356483</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16">
         <v>18</v>
       </c>
       <c r="E16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
         <v>31</v>
       </c>
-      <c r="F16" t="s">
-        <v>32</v>
-      </c>
       <c r="G16">
         <v>5</v>
       </c>
@@ -2162,34 +2067,34 @@
         <v>5</v>
       </c>
       <c r="AE16" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="AF16" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="AG16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>85</v>
+      <c r="A17">
+        <v>16</v>
       </c>
       <c r="B17" s="2">
         <v>44835.689555011573</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17">
         <v>22</v>
       </c>
       <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
         <v>31</v>
       </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
       <c r="G17">
         <v>5</v>
       </c>
@@ -2254,33 +2159,33 @@
         <v>5</v>
       </c>
       <c r="AE17" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="AF17" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="AG17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>88</v>
+      <c r="A18">
+        <v>17</v>
       </c>
       <c r="B18" s="2">
         <v>44835.799018865742</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G18">
         <v>4</v>
@@ -2346,33 +2251,33 @@
         <v>5</v>
       </c>
       <c r="AE18" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="AF18" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="AG18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>92</v>
+      <c r="A19">
+        <v>18</v>
       </c>
       <c r="B19" s="2">
         <v>44835.833253854165</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D19">
         <v>10</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2438,33 +2343,33 @@
         <v>5</v>
       </c>
       <c r="AE19" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AG19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>95</v>
+      <c r="A20">
+        <v>19</v>
       </c>
       <c r="B20" s="2">
         <v>44835.86423767361</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>23</v>
       </c>
       <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" t="s">
         <v>31</v>
-      </c>
-      <c r="F20" t="s">
-        <v>32</v>
       </c>
       <c r="G20">
         <v>4</v>
@@ -2530,33 +2435,33 @@
         <v>5</v>
       </c>
       <c r="AE20" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="AF20" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="AG20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>98</v>
+      <c r="A21">
+        <v>20</v>
       </c>
       <c r="B21" s="2">
         <v>44835.904578009257</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21">
         <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2622,33 +2527,33 @@
         <v>5</v>
       </c>
       <c r="AE21" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AF21" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AG21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>101</v>
+      <c r="A22">
+        <v>21</v>
       </c>
       <c r="B22" s="2">
         <v>44835.918416828703</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D22">
         <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2714,34 +2619,34 @@
         <v>5</v>
       </c>
       <c r="AE22" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AF22" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AG22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>105</v>
+      <c r="A23">
+        <v>22</v>
       </c>
       <c r="B23" s="2">
         <v>44835.921866863428</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D23">
         <v>16</v>
       </c>
       <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
         <v>31</v>
       </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
       <c r="G23">
         <v>5</v>
       </c>
@@ -2806,34 +2711,34 @@
         <v>5</v>
       </c>
       <c r="AE23" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AF23" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AG23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>108</v>
+      <c r="A24">
+        <v>23</v>
       </c>
       <c r="B24" s="2">
         <v>44835.987375335651</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D24">
         <v>22</v>
       </c>
       <c r="E24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" t="s">
         <v>31</v>
       </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
       <c r="G24">
         <v>5</v>
       </c>
@@ -2898,33 +2803,33 @@
         <v>5</v>
       </c>
       <c r="AE24" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="AF24" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="AG24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>111</v>
+      <c r="A25">
+        <v>24</v>
       </c>
       <c r="B25" s="2">
         <v>44836.000867951385</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D25">
         <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -2990,33 +2895,33 @@
         <v>5</v>
       </c>
       <c r="AE25" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="AF25" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="AG25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>113</v>
+      <c r="A26">
+        <v>25</v>
       </c>
       <c r="B26" s="2">
         <v>44836.61945481482</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26">
         <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -3082,33 +2987,33 @@
         <v>4</v>
       </c>
       <c r="AE26" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="AF26" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="AG26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>116</v>
+      <c r="A27">
+        <v>26</v>
       </c>
       <c r="B27" s="2">
         <v>44836.969971099534</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D27">
         <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -3174,34 +3079,34 @@
         <v>5</v>
       </c>
       <c r="AE27" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="AF27" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="AG27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>120</v>
+      <c r="A28">
+        <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>44842.282255613427</v>
       </c>
       <c r="C28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D28">
         <v>23</v>
       </c>
       <c r="E28" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" t="s">
         <v>31</v>
       </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
       <c r="G28">
         <v>5</v>
       </c>
@@ -3266,33 +3171,33 @@
         <v>5</v>
       </c>
       <c r="AE28" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="AF28" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="AG28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>122</v>
+      <c r="A29">
+        <v>28</v>
       </c>
       <c r="B29" s="2">
         <v>44844.152561134259</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D29">
         <v>23</v>
       </c>
       <c r="E29" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" t="s">
         <v>31</v>
-      </c>
-      <c r="F29" t="s">
-        <v>32</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -3358,33 +3263,33 @@
         <v>5</v>
       </c>
       <c r="AE29" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="AF29" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="AG29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>125</v>
+      <c r="A30">
+        <v>29</v>
       </c>
       <c r="B30" s="2">
         <v>44844.704323831014</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D30">
         <v>24</v>
       </c>
       <c r="E30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" t="s">
         <v>31</v>
-      </c>
-      <c r="F30" t="s">
-        <v>32</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3450,33 +3355,33 @@
         <v>5</v>
       </c>
       <c r="AE30" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="AF30" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="AG30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>128</v>
+      <c r="A31">
+        <v>30</v>
       </c>
       <c r="B31" s="2">
         <v>44845.010472071765</v>
       </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D31">
         <v>22</v>
       </c>
       <c r="E31" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" t="s">
         <v>31</v>
-      </c>
-      <c r="F31" t="s">
-        <v>32</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -3542,33 +3447,33 @@
         <v>4</v>
       </c>
       <c r="AE31" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="AF31" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AG31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>132</v>
+      <c r="A32">
+        <v>31</v>
       </c>
       <c r="B32" s="2">
         <v>44846.387997685182</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32">
         <v>24</v>
       </c>
       <c r="E32" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32" t="s">
         <v>31</v>
-      </c>
-      <c r="F32" t="s">
-        <v>32</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -3634,28 +3539,28 @@
         <v>5</v>
       </c>
       <c r="AG32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>133</v>
+      <c r="A33">
+        <v>32</v>
       </c>
       <c r="B33" s="2">
         <v>44846.779351851852</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D33">
         <v>21</v>
       </c>
       <c r="E33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" t="s">
         <v>31</v>
       </c>
-      <c r="F33" t="s">
-        <v>32</v>
-      </c>
       <c r="G33">
         <v>5</v>
       </c>
@@ -3720,28 +3625,28 @@
         <v>5</v>
       </c>
       <c r="AG33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>134</v>
+      <c r="A34">
+        <v>33</v>
       </c>
       <c r="B34" s="2">
         <v>44847.435312499998</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>25</v>
       </c>
       <c r="E34" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" t="s">
         <v>31</v>
       </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
       <c r="G34">
         <v>5</v>
       </c>
@@ -3806,7 +3711,7 @@
         <v>5</v>
       </c>
       <c r="AG34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:33" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4970,7 +4875,7 @@
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="AF12" s="1" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
